--- a/output/stock_quant_scores/TSLA_info.xlsx
+++ b/output/stock_quant_scores/TSLA_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FO2"/>
+  <dimension ref="A1:FS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,230 +1051,250 @@
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1395,28 +1415,28 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>425.85</v>
+        <v>423.3856</v>
       </c>
       <c r="AC2" t="n">
-        <v>429.83</v>
+        <v>428.385</v>
       </c>
       <c r="AD2" t="n">
-        <v>429.0301</v>
+        <v>421.02</v>
       </c>
       <c r="AE2" t="n">
-        <v>443.32</v>
+        <v>440.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>425.85</v>
+        <v>423.3856</v>
       </c>
       <c r="AG2" t="n">
-        <v>429.83</v>
+        <v>428.385</v>
       </c>
       <c r="AH2" t="n">
-        <v>429.0301</v>
+        <v>421.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>443.32</v>
+        <v>440.47</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1425,31 +1445,31 @@
         <v>2.065</v>
       </c>
       <c r="AL2" t="n">
-        <v>266.87952</v>
+        <v>263.7126</v>
       </c>
       <c r="AM2" t="n">
-        <v>136.73456</v>
+        <v>135.92592</v>
       </c>
       <c r="AN2" t="n">
-        <v>71047350</v>
+        <v>100135410</v>
       </c>
       <c r="AO2" t="n">
-        <v>71047349</v>
+        <v>100135410</v>
       </c>
       <c r="AP2" t="n">
-        <v>89756912</v>
+        <v>89789785</v>
       </c>
       <c r="AQ2" t="n">
-        <v>108218280</v>
+        <v>102957270</v>
       </c>
       <c r="AR2" t="n">
-        <v>108218280</v>
+        <v>102957270</v>
       </c>
       <c r="AS2" t="n">
-        <v>434</v>
+        <v>415.63</v>
       </c>
       <c r="AT2" t="n">
-        <v>444</v>
+        <v>458.7</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1458,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1473108377600</v>
+        <v>1464396414976</v>
       </c>
       <c r="AX2" t="n">
         <v>212.11</v>
@@ -1473,13 +1493,13 @@
         <v>0.998667</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.88771</v>
+        <v>15.79375</v>
       </c>
       <c r="BC2" t="n">
-        <v>344.868</v>
+        <v>351.9624</v>
       </c>
       <c r="BD2" t="n">
-        <v>333.523</v>
+        <v>334.4727</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1496,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1350667468800</v>
+        <v>1397597667328</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.063439995</v>
@@ -1508,40 +1528,40 @@
         <v>3325150886</v>
       </c>
       <c r="BM2" t="n">
-        <v>78272760</v>
+        <v>86213226</v>
       </c>
       <c r="BN2" t="n">
-        <v>71986527</v>
+        <v>76710309</v>
       </c>
       <c r="BO2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BP2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.024300002</v>
+        <v>0.025899999</v>
       </c>
       <c r="BR2" t="n">
         <v>0.12560001</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.49416</v>
+        <v>0.49402002</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0278</v>
+        <v>0.0296</v>
       </c>
       <c r="BV2" t="n">
-        <v>3225448889</v>
+        <v>3325150886</v>
       </c>
       <c r="BW2" t="n">
         <v>23.981</v>
       </c>
       <c r="BX2" t="n">
-        <v>18.473791</v>
+        <v>18.364538</v>
       </c>
       <c r="BY2" t="n">
         <v>1735603200</v>
@@ -1559,7 +1579,7 @@
         <v>5879000064</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CE2" t="n">
         <v>3.24</v>
@@ -1573,16 +1593,16 @@
         <v>1661385600</v>
       </c>
       <c r="CH2" t="n">
-        <v>14.567</v>
+        <v>15.073</v>
       </c>
       <c r="CI2" t="n">
-        <v>118.065</v>
+        <v>122.168</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.6568749</v>
+        <v>0.6832932</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
@@ -1590,19 +1610,19 @@
         </is>
       </c>
       <c r="CM2" t="n">
-        <v>443.02</v>
+        <v>440.4</v>
       </c>
       <c r="CN2" t="n">
-        <v>548</v>
+        <v>600</v>
       </c>
       <c r="CO2" t="n">
         <v>115</v>
       </c>
       <c r="CP2" t="n">
-        <v>336.1821</v>
+        <v>341.1821</v>
       </c>
       <c r="CQ2" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="CR2" t="n">
         <v>2.53333</v>
@@ -1712,169 +1732,181 @@
       </c>
       <c r="DV2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DW2" t="n">
-        <v>1758740011</v>
-      </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DX2" t="n">
+        <v>1758931199</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>finmb_27444752</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EB2" t="n">
+      <c r="ED2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="ED2" t="b">
+      <c r="EF2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>4.031554</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>443.02</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+      <c r="EG2" t="n">
+        <v>4.01865</v>
       </c>
       <c r="EH2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="EI2" t="n">
+        <v>440.4</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1277818200000</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.08855225999999999</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>440.01</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.38998413</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>17.0144</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>421.02 - 440.47</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="ES2" t="n">
+        <v>89789785</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>228.29</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1.0762812</v>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>212.11 - 488.54</t>
+        </is>
+      </c>
+      <c r="EW2" t="n">
+        <v>-48.140015</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>-0.09853853</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>68.32932</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1753300800</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1761163200</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1761163200</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1745357400</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1745357400</v>
+      </c>
+      <c r="FE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="FG2" t="n">
         <v>3.24</v>
       </c>
-      <c r="EJ2" t="n">
-        <v>1.69621</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>261.18228</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>98.15197999999999</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.28460738</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>109.49698</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.3283041</v>
-      </c>
-      <c r="EP2" t="n">
+      <c r="FH2" t="n">
+        <v>1.69773</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>259.4052</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>88.43759</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>0.25127</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>105.92731</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.31669942</v>
+      </c>
+      <c r="FN2" t="n">
         <v>15</v>
       </c>
-      <c r="EQ2" t="n">
+      <c r="FO2" t="n">
         <v>0</v>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>2.5 - Hold</t>
         </is>
       </c>
-      <c r="ES2" t="b">
+      <c r="FQ2" t="b">
         <v>0</v>
       </c>
-      <c r="ET2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1277818200000</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>17.169983</v>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>429.0301 - 443.32</t>
-        </is>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="EY2" t="n">
-        <v>89756912</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>230.90999</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1.0886332</v>
-      </c>
-      <c r="FB2" t="inlineStr">
-        <is>
-          <t>212.11 - 488.54</t>
-        </is>
-      </c>
-      <c r="FC2" t="n">
-        <v>-45.52002</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>-0.09317562</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>65.68749</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1753300800</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>1761163200</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>1761163200</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>1745357400</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>1745357400</v>
-      </c>
-      <c r="FK2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="FO2" t="n">
-        <v>7.5373</v>
+      <c r="FS2" t="n">
+        <v>7.7948</v>
       </c>
     </row>
   </sheetData>
